--- a/ParabankAutomation/src/test/resources/TestData.xlsx
+++ b/ParabankAutomation/src/test/resources/TestData.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{246186DA-D069-41D0-9F63-8DF1EFD6D483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{42EA366E-B448-48E0-9350-4E393ACCCDDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{DB95F208-3720-4456-9685-8E2D79731C20}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB95F208-3720-4456-9685-8E2D79731C20}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:O15"/>
+  <oleSize ref="A1:N7"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -79,13 +79,13 @@
     <t>invalidpass</t>
   </si>
   <si>
-    <t>TestNG 12</t>
-  </si>
-  <si>
-    <t>User 12</t>
-  </si>
-  <si>
-    <t>testnguser12</t>
+    <t>testnguser06</t>
+  </si>
+  <si>
+    <t>TestNG 06</t>
+  </si>
+  <si>
+    <t>User 06</t>
   </si>
 </sst>
 </file>
@@ -149,15 +149,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -519,10 +516,10 @@
     </row>
     <row r="2" spans="1:11" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>14</v>
@@ -536,14 +533,14 @@
       <c r="F2" s="2">
         <v>700060</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>5468792130</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>12</v>
@@ -576,7 +573,7 @@
     </row>
     <row r="2" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>12</v>
